--- a/pipeline/credit_rating/output/xhtn_tong_hop_20261027.xlsx
+++ b/pipeline/credit_rating/output/xhtn_tong_hop_20261027.xlsx
@@ -691,7 +691,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1021,7 +1021,7 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1573,7 +1573,7 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2157,7 +2157,7 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2729,7 +2729,7 @@
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2817,7 +2817,7 @@
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3729,7 +3729,7 @@
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4281,7 +4281,7 @@
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:07</t>
+          <t>2026-10-27 02:39:54</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5265,7 +5265,7 @@
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -5387,7 +5387,7 @@
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5809,7 +5809,7 @@
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -5893,7 +5893,7 @@
       <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -7149,7 +7149,7 @@
       <c r="AD60" t="inlineStr"/>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -7237,7 +7237,7 @@
       <c r="AD61" t="inlineStr"/>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -7807,7 +7807,7 @@
       <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8033,7 +8033,7 @@
       <c r="AD68" t="inlineStr"/>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -11115,7 +11115,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -12433,7 +12433,7 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -12647,7 +12647,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -12763,7 +12763,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -13229,7 +13229,7 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -13879,7 +13879,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -13979,7 +13979,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:07</t>
+          <t>2026-10-27 02:39:54</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -14651,7 +14651,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:07</t>
+          <t>2026-10-27 02:39:54</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:07</t>
+          <t>2026-10-27 02:39:54</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -14995,7 +14995,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -15447,7 +15447,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -15675,7 +15675,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -15785,7 +15785,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -15895,7 +15895,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:07</t>
+          <t>2026-10-27 02:39:54</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -16133,7 +16133,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -16505,7 +16505,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -16753,7 +16753,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -16853,7 +16853,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -17101,7 +17101,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -17215,7 +17215,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -17667,7 +17667,7 @@
       </c>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -17895,7 +17895,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -18009,7 +18009,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -18129,7 +18129,7 @@
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -18245,7 +18245,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -18355,7 +18355,7 @@
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -18475,7 +18475,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -18607,7 +18607,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -18735,7 +18735,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -18847,7 +18847,7 @@
       </c>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -18957,7 +18957,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -19067,7 +19067,7 @@
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -19177,7 +19177,7 @@
       </c>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -19287,7 +19287,7 @@
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:07</t>
+          <t>2026-10-27 02:39:54</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -19399,7 +19399,7 @@
       </c>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -19637,7 +19637,7 @@
       <c r="AD169" t="inlineStr"/>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -19877,7 +19877,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -19989,7 +19989,7 @@
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -20101,7 +20101,7 @@
       </c>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -20211,7 +20211,7 @@
       </c>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -20323,7 +20323,7 @@
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -20655,7 +20655,7 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -20771,7 +20771,7 @@
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -20883,7 +20883,7 @@
       </c>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -21003,7 +21003,7 @@
       </c>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -21115,7 +21115,7 @@
       </c>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -21231,7 +21231,7 @@
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -21341,7 +21341,7 @@
       </c>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -21451,7 +21451,7 @@
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -21571,7 +21571,7 @@
       </c>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -21685,7 +21685,7 @@
       </c>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -21799,7 +21799,7 @@
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -21919,7 +21919,7 @@
       </c>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -22145,7 +22145,7 @@
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -22257,7 +22257,7 @@
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -22369,7 +22369,7 @@
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -22483,7 +22483,7 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -22597,7 +22597,7 @@
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -22707,7 +22707,7 @@
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:07</t>
+          <t>2026-10-27 02:39:54</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -22927,7 +22927,7 @@
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -23037,7 +23037,7 @@
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -23151,7 +23151,7 @@
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -23265,7 +23265,7 @@
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -23521,7 +23521,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -23631,7 +23631,7 @@
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -23741,7 +23741,7 @@
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -23861,7 +23861,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -23975,7 +23975,7 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -24085,7 +24085,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -24213,7 +24213,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -24335,7 +24335,7 @@
       <c r="AD210" t="inlineStr"/>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -24463,7 +24463,7 @@
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -24579,7 +24579,7 @@
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -24707,7 +24707,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -24839,7 +24839,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -24953,7 +24953,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -25075,7 +25075,7 @@
       <c r="AD216" t="inlineStr"/>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -25187,7 +25187,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -25287,7 +25287,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -25397,7 +25397,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -25513,7 +25513,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -25629,7 +25629,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -25757,7 +25757,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -25867,7 +25867,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -25981,7 +25981,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -26095,7 +26095,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -26209,7 +26209,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -26319,7 +26319,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -26655,7 +26655,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -26771,7 +26771,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -27111,7 +27111,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -27223,7 +27223,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -27351,7 +27351,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -27461,7 +27461,7 @@
       </c>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -27581,7 +27581,7 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -27703,7 +27703,7 @@
       <c r="AD239" t="inlineStr"/>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -27829,7 +27829,7 @@
       <c r="AD240" t="inlineStr"/>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -27955,7 +27955,7 @@
       <c r="AD241" t="inlineStr"/>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -28071,7 +28071,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -28185,7 +28185,7 @@
       </c>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -28299,7 +28299,7 @@
       </c>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -28413,7 +28413,7 @@
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -28533,7 +28533,7 @@
       </c>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -28653,7 +28653,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -28763,7 +28763,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -28983,7 +28983,7 @@
       </c>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -29099,7 +29099,7 @@
       </c>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -29227,7 +29227,7 @@
       </c>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -29339,7 +29339,7 @@
       </c>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -29451,7 +29451,7 @@
       </c>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -29565,7 +29565,7 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:07</t>
+          <t>2026-10-27 02:39:54</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -29675,7 +29675,7 @@
       </c>
       <c r="AE256" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -29785,7 +29785,7 @@
       </c>
       <c r="AE257" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -29897,7 +29897,7 @@
       </c>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -30007,7 +30007,7 @@
       </c>
       <c r="AE259" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -30127,7 +30127,7 @@
       </c>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -30243,7 +30243,7 @@
       </c>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -30359,7 +30359,7 @@
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -30487,7 +30487,7 @@
       </c>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -30599,7 +30599,7 @@
       </c>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -30711,7 +30711,7 @@
       </c>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -30823,7 +30823,7 @@
       </c>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -30939,7 +30939,7 @@
       </c>
       <c r="AE267" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -31169,7 +31169,7 @@
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -31279,7 +31279,7 @@
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -31399,7 +31399,7 @@
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -31509,7 +31509,7 @@
       </c>
       <c r="AE272" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -31619,7 +31619,7 @@
       </c>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:07</t>
+          <t>2026-10-27 02:39:54</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -31729,7 +31729,7 @@
       </c>
       <c r="AE274" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -31839,7 +31839,7 @@
       </c>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -31953,7 +31953,7 @@
       </c>
       <c r="AE276" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -32063,7 +32063,7 @@
       </c>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -32175,7 +32175,7 @@
       </c>
       <c r="AE278" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -32285,7 +32285,7 @@
       </c>
       <c r="AE279" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -32405,7 +32405,7 @@
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -32517,7 +32517,7 @@
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -32627,7 +32627,7 @@
       </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -32751,7 +32751,7 @@
       </c>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -32875,7 +32875,7 @@
       </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -32985,7 +32985,7 @@
       </c>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -33095,7 +33095,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -33205,7 +33205,7 @@
       </c>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -33317,7 +33317,7 @@
       </c>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -33427,7 +33427,7 @@
       </c>
       <c r="AE289" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -33537,7 +33537,7 @@
       </c>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -33665,7 +33665,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -33771,7 +33771,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -33883,7 +33883,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -33999,7 +33999,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -34225,7 +34225,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -34335,7 +34335,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -34451,7 +34451,7 @@
       </c>
       <c r="AE298" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -34567,7 +34567,7 @@
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -34677,7 +34677,7 @@
       </c>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -34793,7 +34793,7 @@
       </c>
       <c r="AE301" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -34903,7 +34903,7 @@
       </c>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -35013,7 +35013,7 @@
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -35123,7 +35123,7 @@
       </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -35223,7 +35223,7 @@
       </c>
       <c r="AE305" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -35333,7 +35333,7 @@
       </c>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -35445,7 +35445,7 @@
       </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -35555,7 +35555,7 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -35675,7 +35675,7 @@
       </c>
       <c r="AE309" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -35787,7 +35787,7 @@
       </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -35897,7 +35897,7 @@
       </c>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -36009,7 +36009,7 @@
       </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -36125,7 +36125,7 @@
       </c>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -36237,7 +36237,7 @@
       </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -36347,7 +36347,7 @@
       </c>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -36463,7 +36463,7 @@
       </c>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -36573,7 +36573,7 @@
       </c>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -36699,7 +36699,7 @@
       <c r="AD318" t="inlineStr"/>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -36827,7 +36827,7 @@
       </c>
       <c r="AE319" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -36939,7 +36939,7 @@
       </c>
       <c r="AE320" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -37039,7 +37039,7 @@
       </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -37139,7 +37139,7 @@
       </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -37253,7 +37253,7 @@
       </c>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -37367,7 +37367,7 @@
       </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -37467,7 +37467,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -37587,7 +37587,7 @@
       </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -37699,7 +37699,7 @@
       </c>
       <c r="AE327" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -37811,7 +37811,7 @@
       </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -37925,7 +37925,7 @@
       </c>
       <c r="AE329" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -38035,7 +38035,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:07</t>
+          <t>2026-10-27 02:39:54</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -38145,7 +38145,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:07</t>
+          <t>2026-10-27 02:39:54</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -38277,7 +38277,7 @@
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -38405,7 +38405,7 @@
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -38533,7 +38533,7 @@
       </c>
       <c r="AE334" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -38773,7 +38773,7 @@
       </c>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -38885,7 +38885,7 @@
       </c>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -38995,7 +38995,7 @@
       </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -39105,7 +39105,7 @@
       </c>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -39233,7 +39233,7 @@
       </c>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -39343,7 +39343,7 @@
       </c>
       <c r="AE341" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -39471,7 +39471,7 @@
       </c>
       <c r="AE342" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -39583,7 +39583,7 @@
       </c>
       <c r="AE343" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -39695,7 +39695,7 @@
       </c>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -39805,7 +39805,7 @@
       </c>
       <c r="AE345" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -39925,7 +39925,7 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -40049,7 +40049,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -40173,7 +40173,7 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -40297,7 +40297,7 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -40409,7 +40409,7 @@
       </c>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -40525,7 +40525,7 @@
       </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -40637,7 +40637,7 @@
       </c>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -40765,7 +40765,7 @@
       </c>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -40893,7 +40893,7 @@
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -41005,7 +41005,7 @@
       </c>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -41117,7 +41117,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -41227,7 +41227,7 @@
       </c>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -41337,7 +41337,7 @@
       </c>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -41453,7 +41453,7 @@
       </c>
       <c r="AE359" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -41565,7 +41565,7 @@
       </c>
       <c r="AE360" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -41685,7 +41685,7 @@
       </c>
       <c r="AE361" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -41813,7 +41813,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -41929,7 +41929,7 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -42029,7 +42029,7 @@
       </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -42269,7 +42269,7 @@
       </c>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -42503,7 +42503,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -42613,7 +42613,7 @@
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -42723,7 +42723,7 @@
       </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -42833,7 +42833,7 @@
       </c>
       <c r="AE371" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -42953,7 +42953,7 @@
       </c>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -43063,7 +43063,7 @@
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -43173,7 +43173,7 @@
       </c>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -43283,7 +43283,7 @@
       </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -43403,7 +43403,7 @@
       </c>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -43523,7 +43523,7 @@
       </c>
       <c r="AE377" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -43643,7 +43643,7 @@
       </c>
       <c r="AE378" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -43763,7 +43763,7 @@
       </c>
       <c r="AE379" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -43879,7 +43879,7 @@
       </c>
       <c r="AE380" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -43995,7 +43995,7 @@
       </c>
       <c r="AE381" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -44111,7 +44111,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -44223,7 +44223,7 @@
       </c>
       <c r="AE383" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -44335,7 +44335,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -44451,7 +44451,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -44571,7 +44571,7 @@
       </c>
       <c r="AE386" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -44683,7 +44683,7 @@
       </c>
       <c r="AE387" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -44799,7 +44799,7 @@
       </c>
       <c r="AE388" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -44915,7 +44915,7 @@
       </c>
       <c r="AE389" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -45031,7 +45031,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -45147,7 +45147,7 @@
       </c>
       <c r="AE391" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -45257,7 +45257,7 @@
       </c>
       <c r="AE392" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:07</t>
+          <t>2026-10-27 02:39:54</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -45367,7 +45367,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -45483,7 +45483,7 @@
       </c>
       <c r="AE394" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -45595,7 +45595,7 @@
       </c>
       <c r="AE395" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -45705,7 +45705,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -45817,7 +45817,7 @@
       </c>
       <c r="AE397" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -45929,7 +45929,7 @@
       </c>
       <c r="AE398" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -46041,7 +46041,7 @@
       </c>
       <c r="AE399" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -46161,7 +46161,7 @@
       </c>
       <c r="AE400" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -46289,7 +46289,7 @@
       </c>
       <c r="AE401" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -46409,7 +46409,7 @@
       </c>
       <c r="AE402" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -46537,7 +46537,7 @@
       </c>
       <c r="AE403" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -46649,7 +46649,7 @@
       </c>
       <c r="AE404" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -46759,7 +46759,7 @@
       </c>
       <c r="AE405" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -46869,7 +46869,7 @@
       </c>
       <c r="AE406" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -46981,7 +46981,7 @@
       </c>
       <c r="AE407" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -47093,7 +47093,7 @@
       </c>
       <c r="AE408" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -47203,7 +47203,7 @@
       </c>
       <c r="AE409" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -47319,7 +47319,7 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -47429,7 +47429,7 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -47541,7 +47541,7 @@
       </c>
       <c r="AE412" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -47651,7 +47651,7 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -47761,7 +47761,7 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -47889,7 +47889,7 @@
       </c>
       <c r="AE415" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -48001,7 +48001,7 @@
       </c>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -48129,7 +48129,7 @@
       </c>
       <c r="AE417" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -48241,7 +48241,7 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -48351,7 +48351,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -48461,7 +48461,7 @@
       </c>
       <c r="AE420" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -48571,7 +48571,7 @@
       </c>
       <c r="AE421" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -48683,7 +48683,7 @@
       </c>
       <c r="AE422" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -48793,7 +48793,7 @@
       </c>
       <c r="AE423" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -48921,7 +48921,7 @@
       </c>
       <c r="AE424" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -49033,7 +49033,7 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -49143,7 +49143,7 @@
       </c>
       <c r="AE426" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -49253,7 +49253,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -49363,7 +49363,7 @@
       </c>
       <c r="AE428" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -49473,7 +49473,7 @@
       </c>
       <c r="AE429" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -49583,7 +49583,7 @@
       </c>
       <c r="AE430" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -49695,7 +49695,7 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -49823,7 +49823,7 @@
       </c>
       <c r="AE432" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -49933,7 +49933,7 @@
       </c>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -50043,7 +50043,7 @@
       </c>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -50155,7 +50155,7 @@
       </c>
       <c r="AE435" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -50265,7 +50265,7 @@
       </c>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -50377,7 +50377,7 @@
       </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -50505,7 +50505,7 @@
       </c>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -50615,7 +50615,7 @@
       </c>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -50727,7 +50727,7 @@
       </c>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -50837,7 +50837,7 @@
       </c>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -50947,7 +50947,7 @@
       </c>
       <c r="AE442" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -51057,7 +51057,7 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -51157,7 +51157,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -51267,7 +51267,7 @@
       </c>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -51367,7 +51367,7 @@
       </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -51477,7 +51477,7 @@
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -51605,7 +51605,7 @@
       </c>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -51715,7 +51715,7 @@
       </c>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -51825,7 +51825,7 @@
       </c>
       <c r="AE450" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -51935,7 +51935,7 @@
       </c>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -52045,7 +52045,7 @@
       </c>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -52155,7 +52155,7 @@
       </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -52265,7 +52265,7 @@
       </c>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -52375,7 +52375,7 @@
       </c>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -52485,7 +52485,7 @@
       </c>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -52613,7 +52613,7 @@
       </c>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -52725,7 +52725,7 @@
       </c>
       <c r="AE458" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -52825,7 +52825,7 @@
       </c>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -52935,7 +52935,7 @@
       </c>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -53049,7 +53049,7 @@
       </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -53159,7 +53159,7 @@
       </c>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -53259,7 +53259,7 @@
       </c>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
@@ -53371,7 +53371,7 @@
       </c>
       <c r="AE464" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF464" t="inlineStr">
@@ -53483,7 +53483,7 @@
       </c>
       <c r="AE465" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF465" t="inlineStr">
@@ -53593,7 +53593,7 @@
       </c>
       <c r="AE466" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF466" t="inlineStr">
@@ -53705,7 +53705,7 @@
       </c>
       <c r="AE467" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF467" t="inlineStr">
@@ -53817,7 +53817,7 @@
       </c>
       <c r="AE468" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF468" t="inlineStr">
@@ -53927,7 +53927,7 @@
       </c>
       <c r="AE469" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF469" t="inlineStr">
@@ -54055,7 +54055,7 @@
       </c>
       <c r="AE470" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF470" t="inlineStr">
@@ -54187,7 +54187,7 @@
       </c>
       <c r="AE471" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF471" t="inlineStr">
@@ -54319,7 +54319,7 @@
       </c>
       <c r="AE472" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF472" t="inlineStr">
@@ -54451,7 +54451,7 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF473" t="inlineStr">
@@ -54575,7 +54575,7 @@
       </c>
       <c r="AE474" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="AF474" t="inlineStr">
@@ -54687,7 +54687,7 @@
       </c>
       <c r="AE475" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF475" t="inlineStr">
@@ -54787,7 +54787,7 @@
       </c>
       <c r="AE476" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF476" t="inlineStr">
@@ -54907,7 +54907,7 @@
       </c>
       <c r="AE477" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF477" t="inlineStr">
@@ -55023,7 +55023,7 @@
       </c>
       <c r="AE478" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF478" t="inlineStr">
@@ -55135,7 +55135,7 @@
       </c>
       <c r="AE479" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF479" t="inlineStr">
@@ -55257,7 +55257,7 @@
       <c r="AD480" t="inlineStr"/>
       <c r="AE480" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF480" t="inlineStr">
@@ -55369,7 +55369,7 @@
       </c>
       <c r="AE481" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF481" t="inlineStr">
@@ -55479,7 +55479,7 @@
       </c>
       <c r="AE482" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF482" t="inlineStr">
@@ -55589,7 +55589,7 @@
       </c>
       <c r="AE483" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF483" t="inlineStr">
@@ -55699,7 +55699,7 @@
       </c>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF484" t="inlineStr">
@@ -55809,7 +55809,7 @@
       </c>
       <c r="AE485" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF485" t="inlineStr">
@@ -55937,7 +55937,7 @@
       </c>
       <c r="AE486" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF486" t="inlineStr">
@@ -56053,7 +56053,7 @@
       </c>
       <c r="AE487" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF487" t="inlineStr">
@@ -56163,7 +56163,7 @@
       </c>
       <c r="AE488" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF488" t="inlineStr">
@@ -56291,7 +56291,7 @@
       </c>
       <c r="AE489" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF489" t="inlineStr">
@@ -56419,7 +56419,7 @@
       </c>
       <c r="AE490" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF490" t="inlineStr">
@@ -56547,7 +56547,7 @@
       </c>
       <c r="AE491" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF491" t="inlineStr">
@@ -56675,7 +56675,7 @@
       </c>
       <c r="AE492" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF492" t="inlineStr">
@@ -56787,7 +56787,7 @@
       </c>
       <c r="AE493" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF493" t="inlineStr">
@@ -56897,7 +56897,7 @@
       </c>
       <c r="AE494" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF494" t="inlineStr">
@@ -57025,7 +57025,7 @@
       </c>
       <c r="AE495" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF495" t="inlineStr">
@@ -57137,7 +57137,7 @@
       </c>
       <c r="AE496" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF496" t="inlineStr">
@@ -57249,7 +57249,7 @@
       </c>
       <c r="AE497" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF497" t="inlineStr">
@@ -57365,7 +57365,7 @@
       </c>
       <c r="AE498" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF498" t="inlineStr">
@@ -57477,7 +57477,7 @@
       </c>
       <c r="AE499" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF499" t="inlineStr">
@@ -57589,7 +57589,7 @@
       </c>
       <c r="AE500" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF500" t="inlineStr">
@@ -57701,7 +57701,7 @@
       </c>
       <c r="AE501" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF501" t="inlineStr">
@@ -57813,7 +57813,7 @@
       </c>
       <c r="AE502" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF502" t="inlineStr">
@@ -57933,7 +57933,7 @@
       </c>
       <c r="AE503" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF503" t="inlineStr">
@@ -58043,7 +58043,7 @@
       </c>
       <c r="AE504" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF504" t="inlineStr">
@@ -58171,7 +58171,7 @@
       </c>
       <c r="AE505" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF505" t="inlineStr">
@@ -58291,7 +58291,7 @@
       </c>
       <c r="AE506" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF506" t="inlineStr">
@@ -58403,7 +58403,7 @@
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
@@ -58515,7 +58515,7 @@
       </c>
       <c r="AE508" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF508" t="inlineStr">
@@ -58615,7 +58615,7 @@
       </c>
       <c r="AE509" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF509" t="inlineStr">
@@ -58731,7 +58731,7 @@
       </c>
       <c r="AE510" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF510" t="inlineStr">
@@ -58841,7 +58841,7 @@
       </c>
       <c r="AE511" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF511" t="inlineStr">
@@ -58953,7 +58953,7 @@
       </c>
       <c r="AE512" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF512" t="inlineStr">
@@ -59063,7 +59063,7 @@
       </c>
       <c r="AE513" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF513" t="inlineStr">
@@ -59175,7 +59175,7 @@
       </c>
       <c r="AE514" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF514" t="inlineStr">
@@ -59287,7 +59287,7 @@
       </c>
       <c r="AE515" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF515" t="inlineStr">
@@ -59387,7 +59387,7 @@
       </c>
       <c r="AE516" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF516" t="inlineStr">
@@ -59497,7 +59497,7 @@
       </c>
       <c r="AE517" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF517" t="inlineStr">
@@ -59609,7 +59609,7 @@
       </c>
       <c r="AE518" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF518" t="inlineStr">
@@ -59719,7 +59719,7 @@
       </c>
       <c r="AE519" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF519" t="inlineStr">
@@ -59829,7 +59829,7 @@
       </c>
       <c r="AE520" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF520" t="inlineStr">
@@ -59941,7 +59941,7 @@
       </c>
       <c r="AE521" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF521" t="inlineStr">
@@ -60051,7 +60051,7 @@
       </c>
       <c r="AE522" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF522" t="inlineStr">
@@ -60161,7 +60161,7 @@
       </c>
       <c r="AE523" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF523" t="inlineStr">
@@ -60271,7 +60271,7 @@
       </c>
       <c r="AE524" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF524" t="inlineStr">
@@ -60391,7 +60391,7 @@
       </c>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF525" t="inlineStr">
@@ -60515,7 +60515,7 @@
       </c>
       <c r="AE526" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="AF526" t="inlineStr">
@@ -60625,7 +60625,7 @@
       </c>
       <c r="AE527" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF527" t="inlineStr">
@@ -60737,7 +60737,7 @@
       </c>
       <c r="AE528" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF528" t="inlineStr">
@@ -60847,7 +60847,7 @@
       </c>
       <c r="AE529" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF529" t="inlineStr">
@@ -60959,7 +60959,7 @@
       </c>
       <c r="AE530" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF530" t="inlineStr">
@@ -61071,7 +61071,7 @@
       </c>
       <c r="AE531" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF531" t="inlineStr">
@@ -61181,7 +61181,7 @@
       </c>
       <c r="AE532" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF532" t="inlineStr">
@@ -61291,7 +61291,7 @@
       </c>
       <c r="AE533" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF533" t="inlineStr">
@@ -61401,7 +61401,7 @@
       </c>
       <c r="AE534" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF534" t="inlineStr">
@@ -61511,7 +61511,7 @@
       </c>
       <c r="AE535" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF535" t="inlineStr">
@@ -61621,7 +61621,7 @@
       </c>
       <c r="AE536" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF536" t="inlineStr">
@@ -61731,7 +61731,7 @@
       </c>
       <c r="AE537" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF537" t="inlineStr">
@@ -61843,7 +61843,7 @@
       </c>
       <c r="AE538" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF538" t="inlineStr">
@@ -61955,7 +61955,7 @@
       </c>
       <c r="AE539" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF539" t="inlineStr">
@@ -62067,7 +62067,7 @@
       </c>
       <c r="AE540" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF540" t="inlineStr">
@@ -62177,7 +62177,7 @@
       </c>
       <c r="AE541" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF541" t="inlineStr">
@@ -62289,7 +62289,7 @@
       </c>
       <c r="AE542" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF542" t="inlineStr">
@@ -62389,7 +62389,7 @@
       </c>
       <c r="AE543" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF543" t="inlineStr">
@@ -62499,7 +62499,7 @@
       </c>
       <c r="AE544" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF544" t="inlineStr">
@@ -62599,7 +62599,7 @@
       </c>
       <c r="AE545" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF545" t="inlineStr">
@@ -62699,7 +62699,7 @@
       </c>
       <c r="AE546" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF546" t="inlineStr">
@@ -62811,7 +62811,7 @@
       </c>
       <c r="AE547" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF547" t="inlineStr">
@@ -62923,7 +62923,7 @@
       </c>
       <c r="AE548" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF548" t="inlineStr">
@@ -63035,7 +63035,7 @@
       </c>
       <c r="AE549" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF549" t="inlineStr">
@@ -63145,7 +63145,7 @@
       </c>
       <c r="AE550" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF550" t="inlineStr">
@@ -63255,7 +63255,7 @@
       </c>
       <c r="AE551" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF551" t="inlineStr">
@@ -63365,7 +63365,7 @@
       </c>
       <c r="AE552" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF552" t="inlineStr">
@@ -63477,7 +63477,7 @@
       </c>
       <c r="AE553" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF553" t="inlineStr">
@@ -63587,7 +63587,7 @@
       </c>
       <c r="AE554" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF554" t="inlineStr">
@@ -63697,7 +63697,7 @@
       </c>
       <c r="AE555" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF555" t="inlineStr">
@@ -63807,7 +63807,7 @@
       </c>
       <c r="AE556" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF556" t="inlineStr">
@@ -63917,7 +63917,7 @@
       </c>
       <c r="AE557" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF557" t="inlineStr">
@@ -64029,7 +64029,7 @@
       </c>
       <c r="AE558" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF558" t="inlineStr">
@@ -64141,7 +64141,7 @@
       </c>
       <c r="AE559" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF559" t="inlineStr">
@@ -64257,7 +64257,7 @@
       </c>
       <c r="AE560" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF560" t="inlineStr">
@@ -64385,7 +64385,7 @@
       </c>
       <c r="AE561" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF561" t="inlineStr">
@@ -64497,7 +64497,7 @@
       </c>
       <c r="AE562" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF562" t="inlineStr">
@@ -64607,7 +64607,7 @@
       </c>
       <c r="AE563" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF563" t="inlineStr">
@@ -64727,7 +64727,7 @@
       </c>
       <c r="AE564" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF564" t="inlineStr">
@@ -64837,7 +64837,7 @@
       </c>
       <c r="AE565" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF565" t="inlineStr">
@@ -64947,7 +64947,7 @@
       </c>
       <c r="AE566" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF566" t="inlineStr">
@@ -65057,7 +65057,7 @@
       </c>
       <c r="AE567" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF567" t="inlineStr">
@@ -65177,7 +65177,7 @@
       </c>
       <c r="AE568" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF568" t="inlineStr">
@@ -65293,7 +65293,7 @@
       </c>
       <c r="AE569" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF569" t="inlineStr">
@@ -65405,7 +65405,7 @@
       </c>
       <c r="AE570" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF570" t="inlineStr">
@@ -65525,7 +65525,7 @@
       </c>
       <c r="AE571" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF571" t="inlineStr">
@@ -65637,7 +65637,7 @@
       </c>
       <c r="AE572" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF572" t="inlineStr">
@@ -65737,7 +65737,7 @@
       </c>
       <c r="AE573" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF573" t="inlineStr">
@@ -65857,7 +65857,7 @@
       </c>
       <c r="AE574" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF574" t="inlineStr">
@@ -65967,7 +65967,7 @@
       </c>
       <c r="AE575" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF575" t="inlineStr">
@@ -66079,7 +66079,7 @@
       </c>
       <c r="AE576" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF576" t="inlineStr">
@@ -66195,7 +66195,7 @@
       </c>
       <c r="AE577" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF577" t="inlineStr">
@@ -66307,7 +66307,7 @@
       </c>
       <c r="AE578" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF578" t="inlineStr">
@@ -66419,7 +66419,7 @@
       </c>
       <c r="AE579" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF579" t="inlineStr">
@@ -66547,7 +66547,7 @@
       </c>
       <c r="AE580" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF580" t="inlineStr">
@@ -66657,7 +66657,7 @@
       </c>
       <c r="AE581" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF581" t="inlineStr">
@@ -66767,7 +66767,7 @@
       </c>
       <c r="AE582" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF582" t="inlineStr">
@@ -66877,7 +66877,7 @@
       </c>
       <c r="AE583" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF583" t="inlineStr">
@@ -66989,7 +66989,7 @@
       </c>
       <c r="AE584" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF584" t="inlineStr">
@@ -67117,7 +67117,7 @@
       </c>
       <c r="AE585" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF585" t="inlineStr">
@@ -67229,7 +67229,7 @@
       </c>
       <c r="AE586" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF586" t="inlineStr">
@@ -67341,7 +67341,7 @@
       </c>
       <c r="AE587" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF587" t="inlineStr">
@@ -67453,7 +67453,7 @@
       </c>
       <c r="AE588" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF588" t="inlineStr">
@@ -67553,7 +67553,7 @@
       </c>
       <c r="AE589" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF589" t="inlineStr">
@@ -67663,7 +67663,7 @@
       </c>
       <c r="AE590" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF590" t="inlineStr">
@@ -67773,7 +67773,7 @@
       </c>
       <c r="AE591" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF591" t="inlineStr">
@@ -67873,7 +67873,7 @@
       </c>
       <c r="AE592" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF592" t="inlineStr">
@@ -67983,7 +67983,7 @@
       </c>
       <c r="AE593" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF593" t="inlineStr">
@@ -68111,7 +68111,7 @@
       </c>
       <c r="AE594" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF594" t="inlineStr">
@@ -68221,7 +68221,7 @@
       </c>
       <c r="AE595" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF595" t="inlineStr">
@@ -68333,7 +68333,7 @@
       </c>
       <c r="AE596" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF596" t="inlineStr">
@@ -68443,7 +68443,7 @@
       </c>
       <c r="AE597" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF597" t="inlineStr">
@@ -68555,7 +68555,7 @@
       </c>
       <c r="AE598" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF598" t="inlineStr">
@@ -68665,7 +68665,7 @@
       </c>
       <c r="AE599" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF599" t="inlineStr">
@@ -68775,7 +68775,7 @@
       </c>
       <c r="AE600" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF600" t="inlineStr">
@@ -68875,7 +68875,7 @@
       </c>
       <c r="AE601" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF601" t="inlineStr">
@@ -68985,7 +68985,7 @@
       </c>
       <c r="AE602" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF602" t="inlineStr">
@@ -69097,7 +69097,7 @@
       </c>
       <c r="AE603" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF603" t="inlineStr">
@@ -69207,7 +69207,7 @@
       </c>
       <c r="AE604" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF604" t="inlineStr">
@@ -69317,7 +69317,7 @@
       </c>
       <c r="AE605" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF605" t="inlineStr">
@@ -69427,7 +69427,7 @@
       </c>
       <c r="AE606" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF606" t="inlineStr">
@@ -69537,7 +69537,7 @@
       </c>
       <c r="AE607" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF607" t="inlineStr">
@@ -69647,7 +69647,7 @@
       </c>
       <c r="AE608" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF608" t="inlineStr">
@@ -69757,7 +69757,7 @@
       </c>
       <c r="AE609" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF609" t="inlineStr">
@@ -69857,7 +69857,7 @@
       </c>
       <c r="AE610" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF610" t="inlineStr">
@@ -69967,7 +69967,7 @@
       </c>
       <c r="AE611" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF611" t="inlineStr">
@@ -70077,7 +70077,7 @@
       </c>
       <c r="AE612" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF612" t="inlineStr">
@@ -70189,7 +70189,7 @@
       </c>
       <c r="AE613" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF613" t="inlineStr">
@@ -70299,7 +70299,7 @@
       </c>
       <c r="AE614" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF614" t="inlineStr">
@@ -70411,7 +70411,7 @@
       </c>
       <c r="AE615" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF615" t="inlineStr">
@@ -70521,7 +70521,7 @@
       </c>
       <c r="AE616" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF616" t="inlineStr">
@@ -70631,7 +70631,7 @@
       </c>
       <c r="AE617" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF617" t="inlineStr">
@@ -70741,7 +70741,7 @@
       </c>
       <c r="AE618" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF618" t="inlineStr">
@@ -70851,7 +70851,7 @@
       </c>
       <c r="AE619" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF619" t="inlineStr">
@@ -70961,7 +70961,7 @@
       </c>
       <c r="AE620" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF620" t="inlineStr">
@@ -71073,7 +71073,7 @@
       </c>
       <c r="AE621" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF621" t="inlineStr">
@@ -71183,7 +71183,7 @@
       </c>
       <c r="AE622" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF622" t="inlineStr">
@@ -71295,7 +71295,7 @@
       </c>
       <c r="AE623" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF623" t="inlineStr">
@@ -71407,7 +71407,7 @@
       </c>
       <c r="AE624" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF624" t="inlineStr">
@@ -71517,7 +71517,7 @@
       </c>
       <c r="AE625" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF625" t="inlineStr">
@@ -71629,7 +71629,7 @@
       </c>
       <c r="AE626" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF626" t="inlineStr">
@@ -71741,7 +71741,7 @@
       </c>
       <c r="AE627" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF627" t="inlineStr">
@@ -71851,7 +71851,7 @@
       </c>
       <c r="AE628" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF628" t="inlineStr">
@@ -71961,7 +71961,7 @@
       </c>
       <c r="AE629" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF629" t="inlineStr">
@@ -72071,7 +72071,7 @@
       </c>
       <c r="AE630" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF630" t="inlineStr">
@@ -72181,7 +72181,7 @@
       </c>
       <c r="AE631" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF631" t="inlineStr">
@@ -72281,7 +72281,7 @@
       </c>
       <c r="AE632" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF632" t="inlineStr">
@@ -72393,7 +72393,7 @@
       </c>
       <c r="AE633" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF633" t="inlineStr">
@@ -72503,7 +72503,7 @@
       </c>
       <c r="AE634" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF634" t="inlineStr">
@@ -72613,7 +72613,7 @@
       </c>
       <c r="AE635" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF635" t="inlineStr">
@@ -72741,7 +72741,7 @@
       </c>
       <c r="AE636" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF636" t="inlineStr">
@@ -72853,7 +72853,7 @@
       </c>
       <c r="AE637" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF637" t="inlineStr">
@@ -72965,7 +72965,7 @@
       </c>
       <c r="AE638" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF638" t="inlineStr">
@@ -73093,7 +73093,7 @@
       </c>
       <c r="AE639" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF639" t="inlineStr">
@@ -73205,7 +73205,7 @@
       </c>
       <c r="AE640" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF640" t="inlineStr">
@@ -73333,7 +73333,7 @@
       </c>
       <c r="AE641" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF641" t="inlineStr">
@@ -73461,7 +73461,7 @@
       </c>
       <c r="AE642" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:57</t>
+          <t>2026-10-27 02:39:44</t>
         </is>
       </c>
       <c r="AF642" t="inlineStr">
@@ -73573,7 +73573,7 @@
       </c>
       <c r="AE643" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF643" t="inlineStr">
@@ -73685,7 +73685,7 @@
       </c>
       <c r="AE644" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF644" t="inlineStr">
@@ -73795,7 +73795,7 @@
       </c>
       <c r="AE645" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF645" t="inlineStr">
@@ -73907,7 +73907,7 @@
       </c>
       <c r="AE646" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF646" t="inlineStr">
@@ -74017,7 +74017,7 @@
       </c>
       <c r="AE647" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF647" t="inlineStr">
@@ -74127,7 +74127,7 @@
       </c>
       <c r="AE648" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF648" t="inlineStr">
@@ -74239,7 +74239,7 @@
       </c>
       <c r="AE649" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF649" t="inlineStr">
@@ -74351,7 +74351,7 @@
       </c>
       <c r="AE650" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF650" t="inlineStr">
@@ -74463,7 +74463,7 @@
       </c>
       <c r="AE651" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF651" t="inlineStr">
@@ -74573,7 +74573,7 @@
       </c>
       <c r="AE652" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF652" t="inlineStr">
@@ -74683,7 +74683,7 @@
       </c>
       <c r="AE653" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF653" t="inlineStr">
@@ -74795,7 +74795,7 @@
       </c>
       <c r="AE654" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF654" t="inlineStr">
@@ -74907,7 +74907,7 @@
       </c>
       <c r="AE655" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF655" t="inlineStr">
@@ -75017,7 +75017,7 @@
       </c>
       <c r="AE656" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF656" t="inlineStr">
@@ -75129,7 +75129,7 @@
       </c>
       <c r="AE657" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF657" t="inlineStr">
@@ -75239,7 +75239,7 @@
       </c>
       <c r="AE658" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF658" t="inlineStr">
@@ -75339,7 +75339,7 @@
       </c>
       <c r="AE659" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF659" t="inlineStr">
@@ -75449,7 +75449,7 @@
       </c>
       <c r="AE660" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF660" t="inlineStr">
@@ -75561,7 +75561,7 @@
       </c>
       <c r="AE661" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF661" t="inlineStr">
@@ -75671,7 +75671,7 @@
       </c>
       <c r="AE662" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF662" t="inlineStr">
@@ -75783,7 +75783,7 @@
       </c>
       <c r="AE663" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF663" t="inlineStr">
@@ -75893,7 +75893,7 @@
       </c>
       <c r="AE664" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF664" t="inlineStr">
@@ -76003,7 +76003,7 @@
       </c>
       <c r="AE665" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF665" t="inlineStr">
@@ -76113,7 +76113,7 @@
       </c>
       <c r="AE666" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF666" t="inlineStr">
@@ -76223,7 +76223,7 @@
       </c>
       <c r="AE667" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF667" t="inlineStr">
@@ -76333,7 +76333,7 @@
       </c>
       <c r="AE668" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF668" t="inlineStr">
@@ -76445,7 +76445,7 @@
       </c>
       <c r="AE669" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF669" t="inlineStr">
@@ -76555,7 +76555,7 @@
       </c>
       <c r="AE670" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF670" t="inlineStr">
@@ -76665,7 +76665,7 @@
       </c>
       <c r="AE671" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF671" t="inlineStr">
@@ -76775,7 +76775,7 @@
       </c>
       <c r="AE672" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF672" t="inlineStr">
@@ -76887,7 +76887,7 @@
       </c>
       <c r="AE673" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF673" t="inlineStr">
@@ -76997,7 +76997,7 @@
       </c>
       <c r="AE674" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF674" t="inlineStr">
@@ -77109,7 +77109,7 @@
       </c>
       <c r="AE675" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF675" t="inlineStr">
@@ -77221,7 +77221,7 @@
       </c>
       <c r="AE676" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF676" t="inlineStr">
@@ -77321,7 +77321,7 @@
       </c>
       <c r="AE677" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF677" t="inlineStr">
@@ -77431,7 +77431,7 @@
       </c>
       <c r="AE678" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF678" t="inlineStr">
@@ -77543,7 +77543,7 @@
       </c>
       <c r="AE679" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF679" t="inlineStr">
@@ -77655,7 +77655,7 @@
       </c>
       <c r="AE680" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF680" t="inlineStr">
@@ -77767,7 +77767,7 @@
       </c>
       <c r="AE681" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF681" t="inlineStr">
@@ -77879,7 +77879,7 @@
       </c>
       <c r="AE682" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF682" t="inlineStr">
@@ -77989,7 +77989,7 @@
       </c>
       <c r="AE683" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF683" t="inlineStr">
@@ -78099,7 +78099,7 @@
       </c>
       <c r="AE684" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF684" t="inlineStr">
@@ -78211,7 +78211,7 @@
       </c>
       <c r="AE685" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF685" t="inlineStr">
@@ -78321,7 +78321,7 @@
       </c>
       <c r="AE686" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF686" t="inlineStr">
@@ -78433,7 +78433,7 @@
       </c>
       <c r="AE687" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF687" t="inlineStr">
@@ -78533,7 +78533,7 @@
       </c>
       <c r="AE688" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF688" t="inlineStr">
@@ -78643,7 +78643,7 @@
       </c>
       <c r="AE689" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF689" t="inlineStr">
@@ -78755,7 +78755,7 @@
       </c>
       <c r="AE690" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF690" t="inlineStr">
@@ -78865,7 +78865,7 @@
       <c r="AD691" t="inlineStr"/>
       <c r="AE691" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:21</t>
+          <t>2026-10-27 02:40:08</t>
         </is>
       </c>
       <c r="AF691" t="inlineStr">
@@ -78977,7 +78977,7 @@
       </c>
       <c r="AE692" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF692" t="inlineStr">
@@ -79089,7 +79089,7 @@
       </c>
       <c r="AE693" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF693" t="inlineStr">
@@ -79199,7 +79199,7 @@
       </c>
       <c r="AE694" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF694" t="inlineStr">
@@ -79311,7 +79311,7 @@
       </c>
       <c r="AE695" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF695" t="inlineStr">
@@ -79411,7 +79411,7 @@
       </c>
       <c r="AE696" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF696" t="inlineStr">
@@ -79511,7 +79511,7 @@
       </c>
       <c r="AE697" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF697" t="inlineStr">
@@ -79611,7 +79611,7 @@
       </c>
       <c r="AE698" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF698" t="inlineStr">
@@ -79723,7 +79723,7 @@
       </c>
       <c r="AE699" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF699" t="inlineStr">
@@ -79823,7 +79823,7 @@
       </c>
       <c r="AE700" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF700" t="inlineStr">
@@ -79933,7 +79933,7 @@
       </c>
       <c r="AE701" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF701" t="inlineStr">
@@ -80033,7 +80033,7 @@
       </c>
       <c r="AE702" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF702" t="inlineStr">
@@ -80145,7 +80145,7 @@
       </c>
       <c r="AE703" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF703" t="inlineStr">
@@ -80257,7 +80257,7 @@
       </c>
       <c r="AE704" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF704" t="inlineStr">
@@ -80369,7 +80369,7 @@
       </c>
       <c r="AE705" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF705" t="inlineStr">
@@ -80481,7 +80481,7 @@
       </c>
       <c r="AE706" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF706" t="inlineStr">
@@ -80581,7 +80581,7 @@
       </c>
       <c r="AE707" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF707" t="inlineStr">
@@ -80693,7 +80693,7 @@
       </c>
       <c r="AE708" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF708" t="inlineStr">
@@ -80803,7 +80803,7 @@
       </c>
       <c r="AE709" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF709" t="inlineStr">
@@ -80915,7 +80915,7 @@
       </c>
       <c r="AE710" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF710" t="inlineStr">
@@ -81015,7 +81015,7 @@
       </c>
       <c r="AE711" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF711" t="inlineStr">
@@ -81115,7 +81115,7 @@
       </c>
       <c r="AE712" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF712" t="inlineStr">
@@ -81215,7 +81215,7 @@
       </c>
       <c r="AE713" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF713" t="inlineStr">
@@ -81315,7 +81315,7 @@
       </c>
       <c r="AE714" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF714" t="inlineStr">
@@ -81427,7 +81427,7 @@
       </c>
       <c r="AE715" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF715" t="inlineStr">
@@ -81539,7 +81539,7 @@
       </c>
       <c r="AE716" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF716" t="inlineStr">
@@ -81639,7 +81639,7 @@
       </c>
       <c r="AE717" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF717" t="inlineStr">
@@ -81749,7 +81749,7 @@
       </c>
       <c r="AE718" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF718" t="inlineStr">
@@ -81861,7 +81861,7 @@
       </c>
       <c r="AE719" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF719" t="inlineStr">
@@ -81973,7 +81973,7 @@
       </c>
       <c r="AE720" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF720" t="inlineStr">
@@ -82085,7 +82085,7 @@
       </c>
       <c r="AE721" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF721" t="inlineStr">
@@ -82197,7 +82197,7 @@
       </c>
       <c r="AE722" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF722" t="inlineStr">
@@ -82309,7 +82309,7 @@
       </c>
       <c r="AE723" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF723" t="inlineStr">
@@ -82421,7 +82421,7 @@
       </c>
       <c r="AE724" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF724" t="inlineStr">
@@ -82533,7 +82533,7 @@
       </c>
       <c r="AE725" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF725" t="inlineStr">
@@ -82633,7 +82633,7 @@
       </c>
       <c r="AE726" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF726" t="inlineStr">
@@ -82733,7 +82733,7 @@
       </c>
       <c r="AE727" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF727" t="inlineStr">
@@ -82845,7 +82845,7 @@
       </c>
       <c r="AE728" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="AF728" t="inlineStr">
@@ -82945,7 +82945,7 @@
       </c>
       <c r="AE729" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF729" t="inlineStr">
@@ -83045,7 +83045,7 @@
       </c>
       <c r="AE730" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF730" t="inlineStr">
@@ -83145,7 +83145,7 @@
       </c>
       <c r="AE731" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF731" t="inlineStr">
@@ -83255,7 +83255,7 @@
       </c>
       <c r="AE732" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF732" t="inlineStr">
@@ -83355,7 +83355,7 @@
       </c>
       <c r="AE733" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF733" t="inlineStr">
@@ -83465,7 +83465,7 @@
       </c>
       <c r="AE734" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF734" t="inlineStr">
@@ -83547,7 +83547,7 @@
       <c r="AD735" t="inlineStr"/>
       <c r="AE735" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF735" t="inlineStr">
@@ -83629,7 +83629,7 @@
       <c r="AD736" t="inlineStr"/>
       <c r="AE736" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF736" t="inlineStr">
@@ -83711,7 +83711,7 @@
       <c r="AD737" t="inlineStr"/>
       <c r="AE737" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF737" t="inlineStr">
@@ -83793,7 +83793,7 @@
       <c r="AD738" t="inlineStr"/>
       <c r="AE738" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="AF738" t="inlineStr">
